--- a/Decks/Zimone.xlsx
+++ b/Decks/Zimone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8034D9B-CCE6-42C6-8B0E-1F5FC8183CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE04D07C-FBAA-4A69-8798-7E4140AEBD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B1D87B2-7B22-4389-AC3F-EAE6A8AE2B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="114">
   <si>
     <t>Função</t>
   </si>
@@ -246,9 +246,6 @@
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>Blood Artist</t>
   </si>
   <si>
     <t>Lotus Cobra</t>
@@ -933,7 +930,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1200,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1442,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1457,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1472,10 +1469,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1487,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1551,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1642,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,10 +1719,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F61" s="6"/>
     </row>
@@ -1867,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
         <v>67</v>
@@ -1899,10 +1896,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F72" s="6"/>
     </row>
@@ -1915,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F73"/>
     </row>
@@ -1931,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F74"/>
     </row>
@@ -1947,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F75"/>
       <c r="G75"/>
@@ -1964,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F76"/>
     </row>
@@ -1977,13 +1974,13 @@
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F77"/>
     </row>
@@ -1996,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F78" s="6"/>
     </row>
@@ -2012,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F79" s="6"/>
     </row>
@@ -2028,10 +2025,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F80"/>
     </row>
@@ -2044,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F81" s="6"/>
     </row>
@@ -2063,7 +2060,7 @@
         <v>66</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F82" s="6"/>
     </row>
@@ -2076,286 +2073,286 @@
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="D84" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F84"/>
       <c r="G84"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F85"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F96" s="6"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F99" s="6"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F100" s="6"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F101" s="6"/>
     </row>

--- a/Decks/Zimone.xlsx
+++ b/Decks/Zimone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE04D07C-FBAA-4A69-8798-7E4140AEBD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6568806F-EC2C-4247-940D-4087FAFC412D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B1D87B2-7B22-4389-AC3F-EAE6A8AE2B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Rampant Growth</t>
   </si>
   <si>
-    <t>Edge of Autumn</t>
-  </si>
-  <si>
     <t>Farseek</t>
   </si>
   <si>
@@ -176,24 +173,12 @@
     <t>Tireless Tracker</t>
   </si>
   <si>
-    <t>The Hunger Tide Rises</t>
-  </si>
-  <si>
-    <t>Teferi's Ageless Insight</t>
-  </si>
-  <si>
     <t>Phyrexian Arena</t>
   </si>
   <si>
-    <t>Chord of Calling</t>
-  </si>
-  <si>
     <t>Wight of the Reliquary</t>
   </si>
   <si>
-    <t>Token</t>
-  </si>
-  <si>
     <t>Emrakul's Messenger</t>
   </si>
   <si>
@@ -224,12 +209,6 @@
     <t>Zimone, Mystery Unraveler</t>
   </si>
   <si>
-    <t>Homunculus Horde</t>
-  </si>
-  <si>
-    <t>Return</t>
-  </si>
-  <si>
     <t>Bloodghast</t>
   </si>
   <si>
@@ -257,9 +236,6 @@
     <t>Amulet of Vigor</t>
   </si>
   <si>
-    <t>Horizon Explorer</t>
-  </si>
-  <si>
     <t>Retreat to Hagra</t>
   </si>
   <si>
@@ -275,15 +251,9 @@
     <t>Elvish Reclaimer</t>
   </si>
   <si>
-    <t>Ramunap Excavator</t>
-  </si>
-  <si>
     <t>Burgeoning</t>
   </si>
   <si>
-    <t>Ecological Appreciation</t>
-  </si>
-  <si>
     <t>Controle</t>
   </si>
   <si>
@@ -377,7 +347,46 @@
     <t>Minamo, School at Water's Edge</t>
   </si>
   <si>
-    <t>Urza's Saga</t>
+    <t>Folder</t>
+  </si>
+  <si>
+    <t>Pest Rescuer</t>
+  </si>
+  <si>
+    <t>Dina, Essence Brewer</t>
+  </si>
+  <si>
+    <t>Iridescent Vinelasher</t>
+  </si>
+  <si>
+    <t>Vicious Rivalry</t>
+  </si>
+  <si>
+    <t>Dreadhorde Invasion</t>
+  </si>
+  <si>
+    <t>Intruder Alarm</t>
+  </si>
+  <si>
+    <t>Swiftfoot Boots</t>
+  </si>
+  <si>
+    <t>Crop Rotation</t>
+  </si>
+  <si>
+    <t>Grave Researcher // Reanimate</t>
+  </si>
+  <si>
+    <t>Moseo, Vein's New Dean</t>
+  </si>
+  <si>
+    <t>Teacher's Pest</t>
+  </si>
+  <si>
+    <t>Cauldron of Essence</t>
+  </si>
+  <si>
+    <t>Fiend Artisan</t>
   </si>
 </sst>
 </file>
@@ -786,7 +795,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="7" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="7"/>
@@ -833,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B63" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -930,7 +939,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1178,14 +1187,14 @@
         <v>8</v>
       </c>
       <c r="B26" s="5" t="b">
-        <f>C26&lt;&gt;D26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1197,10 +1206,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1259,9 +1268,10 @@
       <c r="C31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="6" t="s">
         <v>34</v>
       </c>
+      <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1274,10 +1284,9 @@
       <c r="C32" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" t="s">
         <v>34</v>
       </c>
-      <c r="F32"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1303,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1356,18 +1365,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F38"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1378,12 +1388,11 @@
         <v>0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1394,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1409,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1424,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1439,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1454,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1469,63 +1478,64 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F46"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47"/>
-      <c r="G47"/>
+        <v>43</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1534,89 +1544,91 @@
       <c r="C49" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="6"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" t="s">
-        <v>47</v>
+        <v>98</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
       </c>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1628,731 +1640,734 @@
       <c r="D55" t="s">
         <v>50</v>
       </c>
-      <c r="F55"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>108</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D57" t="s">
-        <v>52</v>
+        <v>92</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="F57" s="6"/>
-      <c r="G57"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F58" s="6"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C59&lt;&gt;D59</f>
+        <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
-      </c>
-      <c r="F59" s="6"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F60" s="6"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>102</v>
+        <v>54</v>
+      </c>
+      <c r="D61" t="s">
+        <v>54</v>
       </c>
       <c r="F61" s="6"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="F62" s="6"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F63" s="6"/>
+      <c r="G63"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B64:B101" si="1">C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" t="s">
-        <v>59</v>
+        <v>104</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="F64" s="6"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="D65" t="s">
+        <v>57</v>
       </c>
       <c r="F65" s="6"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66"/>
+        <v>58</v>
+      </c>
+      <c r="F66"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F67" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="D67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D68" t="s">
-        <v>64</v>
-      </c>
-      <c r="F68" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C69&lt;&gt;D69</f>
+        <v>1</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
-      </c>
-      <c r="F70"/>
+        <v>66</v>
+      </c>
+      <c r="F70" s="6"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>68</v>
+      <c r="D71" t="s">
+        <v>63</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C72&lt;&gt;D72</f>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D72" t="s">
-        <v>74</v>
-      </c>
-      <c r="F72" s="6"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F74"/>
+      <c r="G74"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F75"/>
-      <c r="G75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
-      </c>
-      <c r="F76"/>
+        <v>68</v>
+      </c>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C77&lt;&gt;D77</f>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
-        <v>75</v>
-      </c>
-      <c r="F77"/>
+        <v>110</v>
+      </c>
+      <c r="F77" s="6"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="D78" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F78" s="6"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
-      </c>
-      <c r="F79" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="E79" t="s">
+        <v>115</v>
+      </c>
+      <c r="F79"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D80" t="s">
-        <v>78</v>
-      </c>
-      <c r="F80"/>
+        <v>71</v>
+      </c>
+      <c r="F80" s="6"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D81" t="s">
-        <v>79</v>
-      </c>
-      <c r="F81" s="6"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D82" t="s">
-        <v>80</v>
-      </c>
-      <c r="F82" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82"/>
+      <c r="G82"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F83"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F84"/>
-      <c r="G84"/>
+        <v>76</v>
+      </c>
+      <c r="D84" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
-      </c>
-      <c r="F85"/>
+        <v>107</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D86" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D87" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D89" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D90" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B91" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D92" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D94" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C95&lt;&gt;D95</f>
+        <v>1</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D95" t="s">
-        <v>95</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F95"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F96" s="6"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F99" s="6"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F100" s="6"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D101" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F101" s="6"/>
     </row>

--- a/Decks/Zimone.xlsx
+++ b/Decks/Zimone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6568806F-EC2C-4247-940D-4087FAFC412D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7918DF7-3A82-42D9-9FD3-1DEE9295004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B1D87B2-7B22-4389-AC3F-EAE6A8AE2B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
   <si>
     <t>Função</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Nemata, Primeval Warden</t>
   </si>
   <si>
-    <t>Zimone, Mystery Unraveler</t>
-  </si>
-  <si>
     <t>Bloodghast</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>Forsaken Miner</t>
   </si>
   <si>
-    <t>Nether Traitor</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>Ashaya, Soul of the Wild</t>
   </si>
   <si>
-    <t>Elvish Reclaimer</t>
-  </si>
-  <si>
     <t>Burgeoning</t>
   </si>
   <si>
@@ -260,9 +251,6 @@
     <t>Dictate of Erebos</t>
   </si>
   <si>
-    <t>Spelunking</t>
-  </si>
-  <si>
     <t>Sothera, the Supervoid</t>
   </si>
   <si>
@@ -365,9 +353,6 @@
     <t>Dreadhorde Invasion</t>
   </si>
   <si>
-    <t>Intruder Alarm</t>
-  </si>
-  <si>
     <t>Swiftfoot Boots</t>
   </si>
   <si>
@@ -383,10 +368,13 @@
     <t>Teacher's Pest</t>
   </si>
   <si>
-    <t>Cauldron of Essence</t>
-  </si>
-  <si>
-    <t>Fiend Artisan</t>
+    <t>Construct a Cosmic Cube</t>
+  </si>
+  <si>
+    <t>Mole Man, Moloid Master</t>
+  </si>
+  <si>
+    <t>Loki, Lord of Misrule</t>
   </si>
 </sst>
 </file>
@@ -939,7 +927,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1191,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1433,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1448,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1463,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1527,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1572,30 +1560,30 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1612,7 +1600,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1628,7 +1616,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1644,7 +1632,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1660,23 +1648,23 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F57" s="6"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1692,22 +1680,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1723,7 +1711,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1739,7 +1727,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1755,155 +1743,152 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" ref="B64:B101" si="1">C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F64" s="6"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F65" s="6"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
-      </c>
-      <c r="E67" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="F68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B69" s="5" t="b">
         <f>C69&lt;&gt;D69</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D70" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F70" s="6"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B72" s="5" t="b">
         <f>C72&lt;&gt;D72</f>
@@ -1918,456 +1903,453 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D74" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F74"/>
       <c r="G74"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F76" s="6"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B77" s="5" t="b">
         <f>C77&lt;&gt;D77</f>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F77" s="6"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F78" s="6"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
-      </c>
-      <c r="E79" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D80" t="s">
-        <v>71</v>
-      </c>
-      <c r="F80" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="F80"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F81" s="6"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F82"/>
-      <c r="G82"/>
+        <v>102</v>
+      </c>
+      <c r="D82" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D83" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="F83"/>
+      <c r="G83"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D84" t="s">
-        <v>76</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F84"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>69</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B85" s="5" t="b">
-        <f>C85&lt;&gt;D85</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D85" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C86&lt;&gt;D86</f>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D88" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D91" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D93" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B95" s="5" t="b">
-        <f>C95&lt;&gt;D95</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="D95" t="s">
-        <v>109</v>
-      </c>
-      <c r="F95"/>
+        <v>81</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F96" s="6"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D97" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F99" s="6"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>82</v>
+      </c>
+      <c r="B100" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B100" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F100" s="6"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F101" s="6"/>
     </row>

--- a/Decks/Zimone.xlsx
+++ b/Decks/Zimone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7918DF7-3A82-42D9-9FD3-1DEE9295004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4B7A88-D6E7-4872-9C50-EB009217ABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B1D87B2-7B22-4389-AC3F-EAE6A8AE2B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="111">
   <si>
     <t>Função</t>
   </si>
@@ -230,9 +230,6 @@
     <t>Amulet of Vigor</t>
   </si>
   <si>
-    <t>Retreat to Hagra</t>
-  </si>
-  <si>
     <t>Ancient Greenwarden</t>
   </si>
   <si>
@@ -326,9 +323,6 @@
     <t>Scrawling Crawler</t>
   </si>
   <si>
-    <t>Cult Conscript</t>
-  </si>
-  <si>
     <t>Dryad Arbor</t>
   </si>
   <si>
@@ -350,15 +344,9 @@
     <t>Vicious Rivalry</t>
   </si>
   <si>
-    <t>Dreadhorde Invasion</t>
-  </si>
-  <si>
     <t>Swiftfoot Boots</t>
   </si>
   <si>
-    <t>Crop Rotation</t>
-  </si>
-  <si>
     <t>Grave Researcher // Reanimate</t>
   </si>
   <si>
@@ -375,6 +363,12 @@
   </si>
   <si>
     <t>Loki, Lord of Misrule</t>
+  </si>
+  <si>
+    <t>Elven Raft-Steerer</t>
+  </si>
+  <si>
+    <t>Great Gilded Boat</t>
   </si>
 </sst>
 </file>
@@ -927,7 +921,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1179,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1406,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1421,10 +1415,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1436,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1451,10 +1445,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1515,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1560,30 +1554,30 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1600,7 +1594,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1616,7 +1610,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1632,7 +1626,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1648,23 +1642,23 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57" s="6"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1680,22 +1674,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1711,7 +1705,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1727,7 +1721,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1743,40 +1737,40 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" ref="B64:B101" si="1">C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F64" s="6"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1792,7 +1786,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1808,14 +1802,14 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1824,49 +1818,49 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B69" s="5" t="b">
         <f>C69&lt;&gt;D69</f>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="F70" s="6"/>
     </row>
@@ -1943,10 +1937,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F75"/>
     </row>
@@ -1959,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F76" s="6"/>
     </row>
@@ -1975,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F77" s="6"/>
     </row>
@@ -1991,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F78" s="6"/>
     </row>
@@ -2007,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F79"/>
     </row>
@@ -2023,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F80"/>
     </row>
@@ -2042,7 +2036,7 @@
         <v>58</v>
       </c>
       <c r="D81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F81" s="6"/>
     </row>
@@ -2055,301 +2049,301 @@
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B83" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="D83" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F83"/>
       <c r="G83"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F84"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B86" s="5" t="b">
         <f>C86&lt;&gt;D86</f>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D88" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D89" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B96" s="5" t="b">
         <f>C96&lt;&gt;D96</f>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F96" s="6"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>81</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F99" s="6"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F100" s="6"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D101" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F101" s="6"/>
     </row>
